--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,16 @@
           <t>AddExp</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>HurtSoundId</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>DeathSoundId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -676,6 +686,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -808,6 +828,16 @@
       <c r="Y5" t="inlineStr">
         <is>
           <t>击杀给英雄的经验(旧 add_exp)</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>死亡语音(同上)</t>
         </is>
       </c>
     </row>
@@ -889,6 +919,16 @@
       </c>
       <c r="Y6" t="n">
         <v>1</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA6"/>
+  <dimension ref="A1:AB6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,11 @@
           <t>DeathSoundId</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -696,6 +701,11 @@
           <t>Sound.SoundId</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -838,6 +848,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>死亡语音(同上)</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
     </row>
@@ -929,6 +944,9 @@
         <is>
           <t>None</t>
         </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +557,41 @@
           <t>Gravity</t>
         </is>
       </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>PatrolInterval</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>PatrolIdleChance</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>PatrolRadius</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>AttackInterval</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>SuperArmor</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>AttackRangeSlack</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -706,6 +741,41 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Monster.MonsterRank</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -853,6 +923,41 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>重力 px/s²(旧 gravity=980 向下)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>巡逻重新决策间隔秒(旧 change_state 计时器 2s)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>站定滞回 px:距离超过 AttackRange+本值才重新追击(新增,防目标被击退几像素就来回切换)</t>
         </is>
       </c>
     </row>
@@ -947,6 +1052,29 @@
       </c>
       <c r="AB6" t="n">
         <v>980</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,70 +524,65 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>AttackRange</t>
+          <t>AttackDesire</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>AttackDesire</t>
+          <t>BehitCalmTime</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>BehitCalmTime</t>
+          <t>AddExp</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>AddExp</t>
+          <t>HurtSoundId</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>HurtSoundId</t>
+          <t>DeathSoundId</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>DeathSoundId</t>
+          <t>Gravity</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t>PatrolInterval</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>PatrolInterval</t>
+          <t>PatrolIdleChance</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>PatrolIdleChance</t>
+          <t>PatrolRadius</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>PatrolRadius</t>
+          <t>AttackInterval</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>AttackInterval</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>SuperArmor</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
-        <is>
-          <t>SuperArmor</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
         <is>
           <t>AttackRangeSlack</t>
         </is>
@@ -713,29 +708,29 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>float</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Sound.SoundId</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Sound.SoundId</t>
-        </is>
-      </c>
       <c r="AB3" t="inlineStr">
         <is>
           <t>float</t>
@@ -743,35 +738,30 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
           <t>float</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>Monster.MonsterRank</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Monster.MonsterRank</t>
+          <t>bool</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -892,72 +882,67 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>进入攻击的距离(旧 attackRange)</t>
+          <t>攻击欲望 0-100(旧 attackDesire)</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>攻击欲望 0-100(旧 attackDesire)</t>
+          <t>受击后僵直秒数(旧 behit_calmtime)</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>受击后僵直秒数(旧 behit_calmtime)</t>
+          <t>击杀给英雄的经验(旧 add_exp)</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>击杀给英雄的经验(旧 add_exp)</t>
+          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
+          <t>死亡语音(同上)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>死亡语音(同上)</t>
+          <t>重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>重力 px/s²(旧 gravity=980 向下)</t>
+          <t>巡逻重新决策间隔秒(旧 change_state 计时器 2s)</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>巡逻重新决策间隔秒(旧 change_state 计时器 2s)</t>
+          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
+          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
+          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>站定滞回 px:距离超过 AttackRange+本值才重新追击(新增,防目标被击退几像素就来回切换)</t>
+          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
         </is>
       </c>
     </row>
@@ -1029,51 +1014,48 @@
         <v>300</v>
       </c>
       <c r="V6" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="W6" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AH6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AH6" t="n">
         <v>25</v>
       </c>
     </row>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
+  <dimension ref="A1:AJ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -587,6 +587,16 @@
           <t>AttackRangeSlack</t>
         </is>
       </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>LoseTargetTime</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>PaceRange</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -766,6 +776,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -943,6 +963,16 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
         </is>
       </c>
     </row>
@@ -1057,6 +1087,12 @@
       </c>
       <c r="AH6" t="n">
         <v>25</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK7"/>
+  <dimension ref="A1:AO7"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" min="3" max="5"/>
@@ -1083,150 +1083,95 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Hp</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Def</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Mdef</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Crit</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Miss</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Lucky</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Toughness</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Htarget</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>CritReduce</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Ar</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Sp</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>RHp</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
+          <t>Stats</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>MoveSpeed</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>SightRange</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>AttackDesire</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>BehitCalmTime</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>AddExp</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>HurtSoundId</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>DeathSoundId</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Gravity</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>PatrolInterval</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>PatrolIdleChance</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>PatrolRadius</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>AttackFirstDelay</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>SuperArmor</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>AttackRangeSlack</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>LoseTargetTime</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>PaceRange</t>
         </is>
@@ -1238,637 +1183,572 @@
           <t>##var</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>MaxHp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MaxMp</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Def</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Mdef</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Crit</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Miss</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Lucky</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Toughness</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Htarget</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>CritReduce</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Ar</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Sp</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Vampirism</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>HpRegen</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>MpRegen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>怪物ID</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>旧怪物编号</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>中文名</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>描述</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Entity.EntityId</t>
+          <t>实体枚举</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>等级(参与等级压制)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>生命(旧 SHp)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>魔法上限</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>攻击(填 0：怪物伤害由招式 FlatPower 决定)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>物防</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>魔防</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>暴击</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>闪避</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>幸运</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>命中(破闪)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>暴击抵抗</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>破甲(减对方物防)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>破魔(减对方魔防)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>吸血(百分点,伤害转生命)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>每秒回血(旧 self_rhp)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>每秒回蓝</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t>索敌距离(旧 mysee)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Sound.SoundId</t>
+          <t>攻击欲望 0-100(旧 attackDesire)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>受击后僵直秒数(旧 behit_calmtime)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>击杀给英雄的经验(旧 add_exp)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>死亡语音(同上)</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>vector2</t>
+          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Monster.MonsterRank</t>
+          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>花果山猴子</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>花果山小怪</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>HuaguoshanMonkey</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>60</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" t="n">
+        <v>80</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>70</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.35,1.0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AL4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>怪物ID</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>旧怪物编号</t>
-        </is>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t>妖猴</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t>花果山精英小怪</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>实体枚举</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>等级(参与等级压制)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>生命(旧 SHp)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>物防</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>魔防</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>暴击</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>闪避</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>幸运</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>韧性(减对方幸运)</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>命中(破闪)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>暴击抵抗</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>破甲(减对方物防)</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>破魔(减对方魔防)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>每秒回血(旧 self_rhp)</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>索敌距离(旧 mysee)</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>攻击欲望 0-100(旧 attackDesire)</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>受击后僵直秒数(旧 behit_calmtime)</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>击杀给英雄的经验(旧 add_exp)</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>死亡语音(同上)</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>重力 px/s²(旧 gravity=980 向下)</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
-        </is>
+          <t>DemonMonkey</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>80</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
-        </is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+          <t>0.35,1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
-        </is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AL5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>60</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>花果山猴子</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>花果山小怪</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HuaguoshanMonkey</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50</v>
-      </c>
-      <c r="J6" t="n">
-        <v>80</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>70</v>
-      </c>
-      <c r="U6" t="n">
-        <v>300</v>
-      </c>
-      <c r="V6" t="n">
-        <v>55</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0.35,1.0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AH6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>妖猴</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>花果山精英小怪</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>DemonMonkey</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>90</v>
-      </c>
-      <c r="I7" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" t="n">
-        <v>80</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>90</v>
-      </c>
-      <c r="U7" t="n">
-        <v>300</v>
-      </c>
-      <c r="V7" t="n">
-        <v>75</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>980</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.35,1.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="AH7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>60</v>
-      </c>
-    </row>
+    <row r="6"/>
+    <row r="7"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:W1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO7"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" min="3" max="5"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -1545,19 +1545,19 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Y4" t="n">
         <v>300</v>
       </c>
       <c r="Z4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -1579,14 +1579,14 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.35,1.0</t>
+          <t>0.5,1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1642,10 +1642,10 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="n">
         <v>300</v>
       </c>
       <c r="Z5" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1715,14 +1715,14 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="AI5" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.35,1.0</t>
+          <t>0.5,1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1743,8 +1743,142 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>大猩猩</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>大猩猩基础配置；关卡配方使用倍率调整生成属性</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gorilla</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>300</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>300</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>980</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>400</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.65,1.0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="AL6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:W1"/>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" min="3" max="5"/>
@@ -1176,6 +1176,26 @@
           <t>PaceRange</t>
         </is>
       </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>SoulPerOrb</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>SoulCount</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>ManaDropChance</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>ManaCount</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1468,6 +1488,26 @@
       <c r="AO3" t="inlineStr">
         <is>
           <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>每颗灵魂值（官方 gxp）</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>灵魂球数量闭区间（官方均匀2～4）</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>蓝球掉落概率（官方12%）</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>触发后蓝球数量闭区间（官方1～3均匀）</t>
         </is>
       </c>
     </row>
@@ -1606,6 +1646,22 @@
       <c r="AO4" t="n">
         <v>60</v>
       </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -1742,6 +1798,22 @@
       <c r="AO5" t="n">
         <v>60</v>
       </c>
+      <c r="AP5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1877,6 +1949,22 @@
       </c>
       <c r="AO6" t="n">
         <v>60</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS6"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
     <col width="11.8181818181818" customWidth="1" min="3" max="5"/>
@@ -1196,6 +1196,16 @@
           <t>ManaCount</t>
         </is>
       </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>MusouDropChance</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>MusouCount</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1508,6 +1518,16 @@
       <c r="AS3" t="inlineStr">
         <is>
           <t>触发后蓝球数量闭区间（官方1～3均匀）</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>白色无双球掉落概率（官方12%）</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>触发后无双球数量闭区间（官方1～3均匀）</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1682,14 @@
           <t>1,3</t>
         </is>
       </c>
+      <c r="AT4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="n">
@@ -1814,6 +1842,14 @@
           <t>1,3</t>
         </is>
       </c>
+      <c r="AT5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
@@ -1962,6 +1998,14 @@
         <v>0.12</v>
       </c>
       <c r="AS6" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>

--- a/Configs/GameConfig/Datas/MonsterConfig.xlsx
+++ b/Configs/GameConfig/Datas/MonsterConfig.xlsx
@@ -1,184 +1,160 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raf11382c9f8f4006"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="21">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
       <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -186,187 +162,156 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39998"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39998"/>
       </patternFill>
     </fill>
   </fills>
@@ -407,7 +352,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,60 +570,59 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="千位分隔" xfId="1"/>
+    <cellStyle name="货币" xfId="2"/>
+    <cellStyle name="百分比" xfId="3"/>
+    <cellStyle name="千位分隔[0]" xfId="4"/>
+    <cellStyle name="货币[0]" xfId="5"/>
+    <cellStyle name="超链接" xfId="6"/>
+    <cellStyle name="已访问的超链接" xfId="7"/>
+    <cellStyle name="注释" xfId="8"/>
+    <cellStyle name="警告文本" xfId="9"/>
+    <cellStyle name="标题" xfId="10"/>
+    <cellStyle name="解释性文本" xfId="11"/>
+    <cellStyle name="标题 1" xfId="12"/>
+    <cellStyle name="标题 2" xfId="13"/>
+    <cellStyle name="标题 3" xfId="14"/>
+    <cellStyle name="标题 4" xfId="15"/>
+    <cellStyle name="输入" xfId="16"/>
+    <cellStyle name="输出" xfId="17"/>
+    <cellStyle name="计算" xfId="18"/>
+    <cellStyle name="检查单元格" xfId="19"/>
+    <cellStyle name="链接单元格" xfId="20"/>
+    <cellStyle name="汇总" xfId="21"/>
+    <cellStyle name="好" xfId="22"/>
+    <cellStyle name="差" xfId="23"/>
+    <cellStyle name="适中" xfId="24"/>
+    <cellStyle name="强调文字颜色 1" xfId="25"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle name="强调文字颜色 2" xfId="29"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle name="强调文字颜色 3" xfId="33"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle name="强调文字颜色 4" xfId="37"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle name="强调文字颜色 5" xfId="41"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle name="强调文字颜色 6" xfId="45"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -914,7 +858,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -923,13 +867,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -963,17 +907,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1028,507 +961,511 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AU6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="11.8181818181818" customWidth="1" min="3" max="5"/>
-    <col width="18.5454545454545" customWidth="1" min="6" max="6"/>
+    <col min="3" max="5" width="11.818181991577148" customWidth="1"/>
+    <col min="6" max="6" width="18.545454025268555" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t xml:space="preserve">Id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>LegacyId</t>
+          <t xml:space="preserve">LegacyId</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>NameCn</t>
+          <t xml:space="preserve">NameCn</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Desc</t>
+          <t xml:space="preserve">Desc</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>EntityId</t>
+          <t xml:space="preserve">EntityId</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Level</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Stats</t>
-        </is>
+          <t xml:space="preserve">Level</t>
+        </is>
+      </c>
+      <c r="H1" t="str">
+        <v>BaseAttributes</v>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>MoveSpeed</t>
+          <t xml:space="preserve">MoveSpeed</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>SightRange</t>
+          <t xml:space="preserve">SightRange</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>AttackDesire</t>
+          <t xml:space="preserve">AttackDesire</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>BehitCalmTime</t>
+          <t xml:space="preserve">BehitCalmTime</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>AddExp</t>
+          <t xml:space="preserve">AddExp</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>HurtSoundId</t>
+          <t xml:space="preserve">HurtSoundId</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>DeathSoundId</t>
+          <t xml:space="preserve">DeathSoundId</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>Gravity</t>
+          <t xml:space="preserve">Gravity</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>PatrolInterval</t>
+          <t xml:space="preserve">PatrolInterval</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>PatrolIdleChance</t>
+          <t xml:space="preserve">PatrolIdleChance</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>PatrolRadius</t>
+          <t xml:space="preserve">PatrolRadius</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>AttackInterval</t>
+          <t xml:space="preserve">AttackInterval</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>AttackFirstDelay</t>
+          <t xml:space="preserve">AttackFirstDelay</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t xml:space="preserve">Rank</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>SuperArmor</t>
+          <t xml:space="preserve">SuperArmor</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>AttackRangeSlack</t>
+          <t xml:space="preserve">AttackRangeSlack</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>LoseTargetTime</t>
+          <t xml:space="preserve">LoseTargetTime</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>PaceRange</t>
+          <t xml:space="preserve">PaceRange</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>SoulPerOrb</t>
+          <t xml:space="preserve">SoulPerOrb</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>SoulCount</t>
+          <t xml:space="preserve">SoulCount</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>ManaDropChance</t>
+          <t xml:space="preserve">ManaDropChance</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>ManaCount</t>
+          <t xml:space="preserve">ManaCount</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>MusouDropChance</t>
+          <t xml:space="preserve">MusouDropChance</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>MusouCount</t>
-        </is>
+          <t xml:space="preserve">MusouCount</t>
+        </is>
+      </c>
+      <c r="AV1" t="str">
+        <v>EquipmentDropChance</v>
+      </c>
+      <c r="AW1" t="str">
+        <v>EquipmentDropPoolId</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##var</t>
+          <t xml:space="preserve">##var</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>MaxHp</t>
+          <t xml:space="preserve">MaxHp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MaxMp</t>
+          <t xml:space="preserve">MaxMp</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t xml:space="preserve">Power</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Def</t>
+          <t xml:space="preserve">Def</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Mdef</t>
+          <t xml:space="preserve">Mdef</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Crit</t>
+          <t xml:space="preserve">Crit</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Miss</t>
+          <t xml:space="preserve">Miss</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t xml:space="preserve">Lucky</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Toughness</t>
+          <t xml:space="preserve">Toughness</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Htarget</t>
+          <t xml:space="preserve">Htarget</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>CritReduce</t>
+          <t xml:space="preserve">CritReduce</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Ar</t>
+          <t xml:space="preserve">Ar</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Sp</t>
+          <t xml:space="preserve">Sp</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Vampirism</t>
+          <t xml:space="preserve">Vampirism</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>HpRegen</t>
+          <t xml:space="preserve">HpRegen</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>MpRegen</t>
+          <t xml:space="preserve">MpRegen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t xml:space="preserve">##</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>怪物ID</t>
+          <t xml:space="preserve">怪物ID</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>旧怪物编号</t>
+          <t xml:space="preserve">旧怪物编号</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>中文名</t>
+          <t xml:space="preserve">中文名</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>描述</t>
+          <t xml:space="preserve">描述</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>实体枚举</t>
+          <t xml:space="preserve">实体枚举</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>等级(参与等级压制)</t>
+          <t xml:space="preserve">等级(参与等级压制)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>生命(旧 SHp)</t>
+          <t xml:space="preserve">生命(旧 SHp)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>魔法上限</t>
+          <t xml:space="preserve">魔法上限</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>攻击(填 0：怪物伤害由招式 FlatPower 决定)</t>
+          <t xml:space="preserve">攻击(填 0：怪物伤害由招式 FlatPower 决定)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>物防</t>
+          <t xml:space="preserve">物防</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>魔防</t>
+          <t xml:space="preserve">魔防</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>暴击</t>
+          <t xml:space="preserve">暴击</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>闪避</t>
+          <t xml:space="preserve">闪避</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>幸运</t>
+          <t xml:space="preserve">幸运</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>韧性(减对方幸运)</t>
+          <t xml:space="preserve">韧性(减对方幸运)</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>命中(破闪)</t>
+          <t xml:space="preserve">命中(破闪)</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>暴击抵抗</t>
+          <t xml:space="preserve">暴击抵抗</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>破甲(减对方物防)</t>
+          <t xml:space="preserve">破甲(减对方物防)</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>破魔(减对方魔防)</t>
+          <t xml:space="preserve">破魔(减对方魔防)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>吸血(百分点,伤害转生命)</t>
+          <t xml:space="preserve">吸血(百分点,伤害转生命)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>每秒回血(旧 self_rhp)</t>
+          <t xml:space="preserve">每秒回血(旧 self_rhp)</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>每秒回蓝</t>
+          <t xml:space="preserve">每秒回蓝</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>移动速度 px/s(旧 speed=8,代码里×10)</t>
+          <t xml:space="preserve">移动速度 px/s(旧 speed=8,代码里×10)</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>索敌距离(旧 mysee)</t>
+          <t xml:space="preserve">索敌距离(旧 mysee)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>攻击欲望 0-100(旧 attackDesire)</t>
+          <t xml:space="preserve">攻击欲望 0-100(旧 attackDesire)</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>受击后僵直秒数(旧 behit_calmtime)</t>
+          <t xml:space="preserve">受击后僵直秒数(旧 behit_calmtime)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>击杀给英雄的经验(旧 add_exp)</t>
+          <t xml:space="preserve">击杀给英雄的经验(旧 add_exp)</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
+          <t xml:space="preserve">受击语音(旧项目怪物无语音素材,填 None;M5 用)</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>死亡语音(同上)</t>
+          <t xml:space="preserve">死亡语音(同上)</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>重力 px/s²(旧 gravity=980 向下)</t>
+          <t xml:space="preserve">重力 px/s²(旧 gravity=980 向下)</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
+          <t xml:space="preserve">巡逻重新决策间隔秒(旧 change_state 计时器 3s)</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
+          <t xml:space="preserve">巡逻决策时原地停留概率 0-100(旧 ran_num&lt;10),其余左右各半</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
+          <t xml:space="preserve">巡逻半径 px:离出生点超出即折返(新增,旧项目无,防走出场地)</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
+          <t xml:space="preserve">近身后普攻判定间隔秒(旧 count%60≈1s,每次按 AttackDesire 掷骰)</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
+          <t xml:space="preserve">进入攻击范围后首次出手判定的随机延迟秒(x=最短,y=最长);出手是概率判定,这里只是反应时间</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
+          <t xml:space="preserve">阶级 Normal/Elite/Boss(旧 is_boss;供 HUD/掉落/结算区分)</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
+          <t xml:space="preserve">霸体:受击不硬直不击退、不打断出招(旧 IsSuperArmor/Monster_18 类保护)</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
+          <t xml:space="preserve">站定滞回 px:目标离开普攻判定盒水平范围超过本值才重新追击(防目标被击退几像素就来回切换)</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
+          <t xml:space="preserve">丢失目标秒:目标水平距离持续超出 SightRange 这么久即放弃、回去巡逻(0=永不丢失)</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
+          <t xml:space="preserve">踱步半幅 px:目标在头顶/平台上够不着时,以目标 x 为中心左右来回走的距离(0=原地等)</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>每颗灵魂值（官方 gxp）</t>
+          <t xml:space="preserve">每颗灵魂值（官方 gxp）</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>灵魂球数量闭区间（官方均匀2～4）</t>
+          <t xml:space="preserve">灵魂球数量闭区间（官方均匀2～4）</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>蓝球掉落概率（官方12%）</t>
+          <t xml:space="preserve">蓝球掉落概率（官方12%）</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>触发后蓝球数量闭区间（官方1～3均匀）</t>
+          <t xml:space="preserve">触发后蓝球数量闭区间（官方1～3均匀）</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>白色无双球掉落概率（官方12%）</t>
+          <t xml:space="preserve">白色无双球掉落概率（官方12%）</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>触发后无双球数量闭区间（官方1～3均匀）</t>
-        </is>
+          <t xml:space="preserve">触发后无双球数量闭区间（官方1～3均匀）</t>
+        </is>
+      </c>
+      <c r="AV3" t="str">
+        <v>装备掉落概率</v>
+      </c>
+      <c r="AW3" t="str">
+        <v>装备池</v>
       </c>
     </row>
     <row r="4">
@@ -1540,17 +1477,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>花果山猴子</t>
+          <t xml:space="preserve">花果山猴子</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>花果山小怪</t>
+          <t xml:space="preserve">花果山小怪</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>HuaguoshanMonkey</t>
+          <t xml:space="preserve">HuaguoshanMonkey</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1621,12 +1558,12 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AE4" t="n">
@@ -1646,12 +1583,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5,1.0</t>
+          <t xml:space="preserve">0.5,1.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="AL4" t="b">
@@ -1671,7 +1608,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t xml:space="preserve">2,4</t>
         </is>
       </c>
       <c r="AR4" t="n">
@@ -1679,7 +1616,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t xml:space="preserve">1,3</t>
         </is>
       </c>
       <c r="AT4" t="n">
@@ -1687,8 +1624,14 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>1,3</t>
-        </is>
+          <t xml:space="preserve">1,3</t>
+        </is>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW4" t="str">
+        <v>粗糙装备</v>
       </c>
     </row>
     <row r="5">
@@ -1700,17 +1643,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>妖猴</t>
+          <t xml:space="preserve">妖猴</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>花果山精英小怪</t>
+          <t xml:space="preserve">花果山精英小怪</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DemonMonkey</t>
+          <t xml:space="preserve">DemonMonkey</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1781,12 +1724,12 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AE5" t="n">
@@ -1806,12 +1749,12 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5,1.0</t>
+          <t xml:space="preserve">0.5,1.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="AL5" t="b">
@@ -1831,7 +1774,7 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t xml:space="preserve">2,4</t>
         </is>
       </c>
       <c r="AR5" t="n">
@@ -1839,7 +1782,7 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t xml:space="preserve">1,3</t>
         </is>
       </c>
       <c r="AT5" t="n">
@@ -1847,8 +1790,14 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>1,3</t>
-        </is>
+          <t xml:space="preserve">1,3</t>
+        </is>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW5" t="str">
+        <v>粗糙装备</v>
       </c>
     </row>
     <row r="6">
@@ -1860,17 +1809,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>大猩猩</t>
+          <t xml:space="preserve">大猩猩</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>大猩猩基础配置；关卡配方使用倍率调整生成属性</t>
+          <t xml:space="preserve">大猩猩基础配置；关卡配方使用倍率调整生成属性</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gorilla</t>
+          <t xml:space="preserve">Gorilla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1941,12 +1890,12 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="AE6" t="n">
@@ -1966,12 +1915,12 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.65,1.0</t>
+          <t xml:space="preserve">0.65,1.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t xml:space="preserve">Normal</t>
         </is>
       </c>
       <c r="AL6" t="b">
@@ -1991,7 +1940,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t xml:space="preserve">2,4</t>
         </is>
       </c>
       <c r="AR6" t="n">
@@ -1999,7 +1948,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t xml:space="preserve">1,3</t>
         </is>
       </c>
       <c r="AT6" t="n">
@@ -2007,14 +1956,20 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>1,3</t>
-        </is>
+          <t xml:space="preserve">1,3</t>
+        </is>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW6" t="str">
+        <v>粗糙装备</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="H1:W1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>